--- a/src/data/settings.xlsx
+++ b/src/data/settings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7C3849-CF03-4764-988B-27B8291B5631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39155C05-F508-40B2-A995-EB3C48B0E57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="396" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
   <si>
     <t>Value</t>
   </si>
@@ -53,47 +53,245 @@
     <t>Key</t>
   </si>
   <si>
-    <t>site_name</t>
-  </si>
-  <si>
     <t>currency_symbol</t>
   </si>
   <si>
-    <t>support_email</t>
-  </si>
-  <si>
-    <t>JK Enterprises</t>
-  </si>
-  <si>
     <t>INR</t>
   </si>
   <si>
-    <t>care@haryana.tools</t>
-  </si>
-  <si>
-    <t>general</t>
-  </si>
-  <si>
-    <t>localization</t>
-  </si>
-  <si>
-    <t>contact</t>
-  </si>
-  <si>
-    <t>Website main title</t>
-  </si>
-  <si>
-    <t>Primary currency indicator</t>
-  </si>
-  <si>
-    <t>Customer service email</t>
+    <t>site_title</t>
+  </si>
+  <si>
+    <t>Haryana.Tools - Power Tools, Hand Tools &amp; Solar Solutions</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>The main website title displayed in browser tabs and search engine results.</t>
+  </si>
+  <si>
+    <t>site_tagline</t>
+  </si>
+  <si>
+    <t>Your Ultimate Industrial &amp; Workshop Equipment Partner</t>
+  </si>
+  <si>
+    <t>Short catchy tagline describing the platform's core offering.</t>
+  </si>
+  <si>
+    <t>contact_email</t>
+  </si>
+  <si>
+    <t>support@haryana.tools</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Primary customer support and business inquiry email address.</t>
+  </si>
+  <si>
+    <t>contact_phone</t>
+  </si>
+  <si>
+    <t>Official helpline and customer service telephone number.</t>
+  </si>
+  <si>
+    <t>office_address</t>
+  </si>
+  <si>
+    <t>Industrial Area, Pehowa, Haryana, India</t>
+  </si>
+  <si>
+    <t>Physical headquarters or registered office location.</t>
+  </si>
+  <si>
+    <t>₹</t>
+  </si>
+  <si>
+    <t>Localization</t>
+  </si>
+  <si>
+    <t>Default currency symbol used across product listings and pricing.</t>
+  </si>
+  <si>
+    <t>currency_code</t>
+  </si>
+  <si>
+    <t>ISO standard currency code for financial calculations and transactions.</t>
+  </si>
+  <si>
+    <t>tax_rate_gst</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>Default Goods and Services Tax (GST) percentage applied to applicable items.</t>
+  </si>
+  <si>
+    <t>maintenance_mode</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Flag to toggle the website into maintenance mode (true/false).</t>
+  </si>
+  <si>
+    <t>items_per_page</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Number of product listings displayed per page in catalog and search views.</t>
+  </si>
+  <si>
+    <t>seo_meta_keywords</t>
+  </si>
+  <si>
+    <t>power tools, hand tools, solar panels, car care products, haryana tools</t>
+  </si>
+  <si>
+    <t>SEO</t>
+  </si>
+  <si>
+    <t>Default comma-separated keywords for search engine optimization.</t>
+  </si>
+  <si>
+    <t>google_analytics_id</t>
+  </si>
+  <si>
+    <t>G-HARYANATOOLS</t>
+  </si>
+  <si>
+    <t>Analytics</t>
+  </si>
+  <si>
+    <t>Tracking ID for Google Analytics traffic and user behavior monitoring.</t>
+  </si>
+  <si>
+    <t>facebook_pixel_id</t>
+  </si>
+  <si>
+    <t>Tracking pixel ID for Facebook ad campaigns and conversion tracking.</t>
+  </si>
+  <si>
+    <t>free_shipping_threshold</t>
+  </si>
+  <si>
+    <t>Shipping</t>
+  </si>
+  <si>
+    <t>Minimum order value in INR required to qualify for free delivery.</t>
+  </si>
+  <si>
+    <t>standard_shipping_fee</t>
+  </si>
+  <si>
+    <t>Default flat shipping fee applied to orders below the free shipping threshold.</t>
+  </si>
+  <si>
+    <t>cod_enabled</t>
+  </si>
+  <si>
+    <t>Checkout</t>
+  </si>
+  <si>
+    <t>Flag enabling or disabling Cash on Delivery as a payment option.</t>
+  </si>
+  <si>
+    <t>max_cod_amount</t>
+  </si>
+  <si>
+    <t>Maximum cart order value allowed for Cash on Delivery transactions.</t>
+  </si>
+  <si>
+    <t>social_facebook</t>
+  </si>
+  <si>
+    <t>https://facebook.com/haryana.tools</t>
+  </si>
+  <si>
+    <t>Social</t>
+  </si>
+  <si>
+    <t>Official Facebook page link for brand engagement and updates.</t>
+  </si>
+  <si>
+    <t>social_instagram</t>
+  </si>
+  <si>
+    <t>https://instagram.com/haryana.tools</t>
+  </si>
+  <si>
+    <t>Official Instagram handle link for product showcases and reels.</t>
+  </si>
+  <si>
+    <t>social_linkedin</t>
+  </si>
+  <si>
+    <t>https://linkedin.com/company/haryana-tools</t>
+  </si>
+  <si>
+    <t>Official LinkedIn company profile for B2B networking and hiring.</t>
+  </si>
+  <si>
+    <t>social_twitter</t>
+  </si>
+  <si>
+    <t>https://twitter.com/haryana_tools</t>
+  </si>
+  <si>
+    <t>Official Twitter/X handle link for company announcements and support.</t>
+  </si>
+  <si>
+    <t>social_youtube</t>
+  </si>
+  <si>
+    <t>https://youtube.com/@haryana-tools</t>
+  </si>
+  <si>
+    <t>Official YouTube channel link for product demonstrations and video tutorials.</t>
+  </si>
+  <si>
+    <t>invoice_prefix</t>
+  </si>
+  <si>
+    <t>HT-2026-</t>
+  </si>
+  <si>
+    <t>Billing</t>
+  </si>
+  <si>
+    <t>Prefix code added to the beginning of all generated customer invoice numbers.</t>
+  </si>
+  <si>
+    <t>return_window_days</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>Number of days allowed for customers to request product returns or replacements.</t>
+  </si>
+  <si>
+    <t>low_stock_threshold</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>Stock quantity level that triggers low inventory email notifications to admins.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,17 +300,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -123,7 +329,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -131,15 +337,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -475,69 +703,389 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="76.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2">
+        <f>91-9876543210</f>
+        <v>-9876543119</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2">
+        <v>18</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="2">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="2">
+        <v>123456789012345</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="2">
+        <v>5000</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="2">
+        <v>150</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="2">
+        <v>25000</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="2">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="C25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="2">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
+      <c r="C26" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{B84143C6-265A-4065-A6E3-233C59E0D1B0}"/>
+    <hyperlink ref="B19" r:id="rId1" display="https://www.google.com/search?q=https://facebook.com/haryana.tools" xr:uid="{B2F93F00-367A-47A5-98C2-351E0009479E}"/>
+    <hyperlink ref="B20" r:id="rId2" display="https://www.google.com/search?q=https://instagram.com/haryana.tools" xr:uid="{85D8B726-EA89-43AC-BEB8-76AC94256C6F}"/>
+    <hyperlink ref="B21" r:id="rId3" display="https://www.google.com/search?q=https://linkedin.com/company/haryana-tools" xr:uid="{20F375B5-FB4B-4AA0-A9D8-12D6F79C3399}"/>
+    <hyperlink ref="B22" r:id="rId4" display="https://www.google.com/search?q=https://twitter.com/haryana_tools" xr:uid="{06445CFB-7139-468B-81BB-0E2AA02C30CE}"/>
+    <hyperlink ref="B23" r:id="rId5" display="https://www.google.com/search?q=https://youtube.com/%40haryana-tools" xr:uid="{E47D4DDD-F994-4569-B201-1E261DDD14EE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>